--- a/research/traditional_assets/database/data/turkey/turkey_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.164</v>
+        <v>0.397</v>
       </c>
       <c r="E2">
-        <v>0.1455</v>
+        <v>0.493</v>
       </c>
       <c r="F2">
-        <v>0.338</v>
+        <v>0.422</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4959.8</v>
+        <v>13373.3</v>
       </c>
       <c r="L2">
-        <v>0.2991128774492362</v>
+        <v>0.4433294878934946</v>
       </c>
       <c r="M2">
-        <v>320.537</v>
+        <v>427.008</v>
       </c>
       <c r="N2">
-        <v>0.01358029241921612</v>
+        <v>0.008867752513348105</v>
       </c>
       <c r="O2">
-        <v>0.06462700108875358</v>
+        <v>0.03192989015426259</v>
       </c>
       <c r="P2">
-        <v>320.537</v>
+        <v>360.308</v>
       </c>
       <c r="Q2">
-        <v>0.01358029241921612</v>
+        <v>0.007482581526761628</v>
       </c>
       <c r="R2">
-        <v>0.06462700108875358</v>
+        <v>0.0269423403348463</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>66.70000000000002</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.156203162470024</v>
       </c>
       <c r="U2">
-        <v>46992.5</v>
+        <v>51234.4</v>
       </c>
       <c r="V2">
-        <v>1.990946104537116</v>
+        <v>1.063994068893047</v>
       </c>
       <c r="W2">
-        <v>0.1202311843714934</v>
+        <v>0.2849709540610856</v>
       </c>
       <c r="X2">
-        <v>0.3326691447711166</v>
+        <v>0.2556498960457627</v>
       </c>
       <c r="Y2">
-        <v>-0.2124379603996232</v>
+        <v>0.02932105801532287</v>
       </c>
       <c r="Z2">
-        <v>0.1266430460612498</v>
+        <v>0.2225892327837866</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0970369457474292</v>
+        <v>0.1481846444259929</v>
       </c>
       <c r="AC2">
-        <v>-0.0970369457474292</v>
+        <v>-0.1481846444259929</v>
       </c>
       <c r="AD2">
-        <v>119778.6</v>
+        <v>96852.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>119778.6</v>
+        <v>96852.3</v>
       </c>
       <c r="AG2">
-        <v>72786.10000000001</v>
+        <v>45617.9</v>
       </c>
       <c r="AH2">
-        <v>0.8353827580507136</v>
+        <v>0.6679229434530624</v>
       </c>
       <c r="AI2">
-        <v>0.7245468051334663</v>
+        <v>0.6618691122553927</v>
       </c>
       <c r="AJ2">
-        <v>0.7551271304254004</v>
+        <v>0.4864829989719614</v>
       </c>
       <c r="AK2">
-        <v>0.6151490795933494</v>
+        <v>0.4796981190803926</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.168</v>
+        <v>0.42</v>
       </c>
       <c r="E3">
-        <v>0.301</v>
+        <v>0.493</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,10 +731,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>371.7</v>
+        <v>689.7</v>
       </c>
       <c r="L3">
-        <v>0.3667127071823204</v>
+        <v>0.4288645690834473</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3162.3</v>
+        <v>3918</v>
       </c>
       <c r="V3">
-        <v>0.3171338314195457</v>
+        <v>0.4090709766334649</v>
       </c>
       <c r="W3">
-        <v>0.1607768502097842</v>
+        <v>0.2831862040648738</v>
       </c>
       <c r="X3">
-        <v>0.1140769266249314</v>
+        <v>0.1604413138121452</v>
       </c>
       <c r="Y3">
-        <v>0.0466999235848528</v>
+        <v>0.1227448902527286</v>
       </c>
       <c r="Z3">
-        <v>0.1093360660158568</v>
+        <v>0.180350113826244</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08860513224236555</v>
+        <v>0.1355010849333974</v>
       </c>
       <c r="AC3">
-        <v>-0.08860513224236555</v>
+        <v>-0.1355010849333974</v>
       </c>
       <c r="AD3">
-        <v>9643.9</v>
+        <v>7484.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9643.9</v>
+        <v>7484.3</v>
       </c>
       <c r="AG3">
-        <v>6481.599999999999</v>
+        <v>3566.3</v>
       </c>
       <c r="AH3">
-        <v>0.4916494183141817</v>
+        <v>0.4386505764237697</v>
       </c>
       <c r="AI3">
-        <v>0.7983096586205755</v>
+        <v>0.7834174220696297</v>
       </c>
       <c r="AJ3">
-        <v>0.3939439983954391</v>
+        <v>0.2713232553008574</v>
       </c>
       <c r="AK3">
-        <v>0.726791581166392</v>
+        <v>0.6328388401888065</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.182</v>
+        <v>0.38</v>
       </c>
       <c r="E4">
-        <v>0.158</v>
+        <v>0.469</v>
       </c>
       <c r="F4">
-        <v>0.2</v>
+        <v>0.489</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,28 +853,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1137.6</v>
+        <v>2299.6</v>
       </c>
       <c r="L4">
-        <v>0.3409765308875101</v>
+        <v>0.5228859228268037</v>
       </c>
       <c r="M4">
-        <v>70.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="N4">
-        <v>0.01958104376446961</v>
+        <v>0.01047104888467015</v>
       </c>
       <c r="O4">
-        <v>0.06170886075949368</v>
+        <v>0.03070099147677857</v>
       </c>
       <c r="P4">
-        <v>70.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="Q4">
-        <v>0.01958104376446961</v>
+        <v>0.01047104888467015</v>
       </c>
       <c r="R4">
-        <v>0.06170886075949368</v>
+        <v>0.03070099147677857</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8225.799999999999</v>
+        <v>9332.799999999999</v>
       </c>
       <c r="V4">
-        <v>2.294440880310173</v>
+        <v>1.384195538680588</v>
       </c>
       <c r="W4">
-        <v>0.1451020408163265</v>
+        <v>0.2883619446499555</v>
       </c>
       <c r="X4">
-        <v>0.1930994612339764</v>
+        <v>0.1836293911594707</v>
       </c>
       <c r="Y4">
-        <v>-0.04799742041764984</v>
+        <v>0.1047325534904848</v>
       </c>
       <c r="Z4">
-        <v>0.2692372748407156</v>
+        <v>0.4599505045190274</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0927840048678707</v>
+        <v>0.1403369817751993</v>
       </c>
       <c r="AC4">
-        <v>-0.0927840048678707</v>
+        <v>-0.1403369817751993</v>
       </c>
       <c r="AD4">
-        <v>9813.5</v>
+        <v>7942.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>9813.5</v>
+        <v>7942.2</v>
       </c>
       <c r="AG4">
-        <v>1587.700000000001</v>
+        <v>-1390.599999999999</v>
       </c>
       <c r="AH4">
-        <v>0.7324272685205917</v>
+        <v>0.5408523214796453</v>
       </c>
       <c r="AI4">
-        <v>0.5506829175224179</v>
+        <v>0.5277349564108017</v>
       </c>
       <c r="AJ4">
-        <v>0.3069324157129601</v>
+        <v>-0.2598378115774131</v>
       </c>
       <c r="AK4">
-        <v>0.1654750489848669</v>
+        <v>-0.2432479708928071</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ICBC Turkey Bank A.S. (IBSE:ICBCT)</t>
+          <t>Albaraka Türk Katilim Bankasi A.S. (IBSE:ALBRK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.321</v>
+        <v>0.371</v>
       </c>
       <c r="E5">
-        <v>0.516</v>
+        <v>0.478</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>22.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="L5">
-        <v>0.2352941176470588</v>
+        <v>0.2828481510621558</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1002,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>486.7</v>
+        <v>1340.4</v>
       </c>
       <c r="V5">
-        <v>1.415236987496365</v>
+        <v>2.994638069705094</v>
       </c>
       <c r="W5">
-        <v>0.1250685682940209</v>
+        <v>0.1509235936188077</v>
       </c>
       <c r="X5">
-        <v>0.1684670133809644</v>
+        <v>0.1912788510663939</v>
       </c>
       <c r="Y5">
-        <v>-0.04339844508694357</v>
+        <v>-0.04035525744758614</v>
       </c>
       <c r="Z5">
-        <v>0.08856594461200988</v>
+        <v>1.885113388606264</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.09393386939585689</v>
+        <v>0.1415679062302372</v>
       </c>
       <c r="AC5">
-        <v>-0.09393386939585689</v>
+        <v>-0.1415679062302372</v>
       </c>
       <c r="AD5">
-        <v>751.6</v>
+        <v>585.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>751.6</v>
+        <v>585.8</v>
       </c>
       <c r="AG5">
-        <v>264.9</v>
+        <v>-754.6000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.6860794157918759</v>
+        <v>0.5668666537642731</v>
       </c>
       <c r="AI5">
-        <v>0.8051419389394752</v>
+        <v>0.5308563661078387</v>
       </c>
       <c r="AJ5">
-        <v>0.4351182654402103</v>
+        <v>2.457980456026058</v>
       </c>
       <c r="AK5">
-        <v>0.592882721575649</v>
+        <v>3.185310257492612</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Akbank T.A.S. (IBSE:AKBNK)</t>
+          <t>Sekerbank T.A.S. (IBSE:SKBNK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,13 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.172</v>
+        <v>0.359</v>
       </c>
       <c r="E6">
-        <v>0.144</v>
-      </c>
-      <c r="F6">
-        <v>0.324</v>
+        <v>0.578</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1035.1</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L6">
-        <v>0.4015906886517943</v>
+        <v>0.2905951506245408</v>
       </c>
       <c r="M6">
-        <v>70.5</v>
+        <v>0.108</v>
       </c>
       <c r="N6">
-        <v>0.02486158620446451</v>
+        <v>0.0003550295857988166</v>
       </c>
       <c r="O6">
-        <v>0.06810936141435611</v>
+        <v>0.001365360303413401</v>
       </c>
       <c r="P6">
-        <v>70.5</v>
+        <v>0.108</v>
       </c>
       <c r="Q6">
-        <v>0.02486158620446451</v>
+        <v>0.0003550295857988166</v>
       </c>
       <c r="R6">
-        <v>0.06810936141435611</v>
+        <v>0.001365360303413401</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1127,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>4286.4</v>
+        <v>807.6</v>
       </c>
       <c r="V6">
-        <v>1.511584441231442</v>
+        <v>2.65483234714004</v>
       </c>
       <c r="W6">
-        <v>0.1354399738305528</v>
+        <v>0.2532010243277849</v>
       </c>
       <c r="X6">
-        <v>0.3301040196880687</v>
+        <v>0.2327585668735655</v>
       </c>
       <c r="Y6">
-        <v>-0.1946640458575159</v>
+        <v>0.02044245745421938</v>
       </c>
       <c r="Z6">
-        <v>0.1424096092644979</v>
+        <v>0.8081947743467931</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.09638854392540233</v>
+        <v>0.1463846465027526</v>
       </c>
       <c r="AC6">
-        <v>-0.09638854392540233</v>
+        <v>-0.1463846465027526</v>
       </c>
       <c r="AD6">
-        <v>16464.9</v>
+        <v>613.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>16464.9</v>
+        <v>613.9</v>
       </c>
       <c r="AG6">
-        <v>12178.5</v>
+        <v>-193.7</v>
       </c>
       <c r="AH6">
-        <v>0.8530771064111996</v>
+        <v>0.6686635442762227</v>
       </c>
       <c r="AI6">
-        <v>0.6755080187576157</v>
+        <v>0.6967427079786631</v>
       </c>
       <c r="AJ6">
-        <v>0.8111321282519216</v>
+        <v>-1.75294117647059</v>
       </c>
       <c r="AK6">
-        <v>0.6062665213040817</v>
+        <v>-2.635374149659866</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sekerbank T.A.S. (IBSE:SKBNK)</t>
+          <t>Akbank T.A.S. (IBSE:AKBNK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,10 +1198,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.1</v>
+        <v>0.479</v>
       </c>
       <c r="E7">
-        <v>0.138</v>
+        <v>0.499</v>
+      </c>
+      <c r="F7">
+        <v>0.422</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,28 +1219,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>16</v>
+        <v>2321.5</v>
       </c>
       <c r="L7">
-        <v>0.08465608465608465</v>
+        <v>0.5087550130393811</v>
       </c>
       <c r="M7">
-        <v>0.169</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="N7">
-        <v>0.001187631763879129</v>
+        <v>0.01203821304323817</v>
       </c>
       <c r="O7">
-        <v>0.0105625</v>
+        <v>0.0281714408787422</v>
       </c>
       <c r="P7">
-        <v>0.169</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Q7">
-        <v>0.001187631763879129</v>
+        <v>0.01203821304323817</v>
       </c>
       <c r="R7">
-        <v>0.0105625</v>
+        <v>0.0281714408787422</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1249,55 +1249,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>817.1</v>
+        <v>3271.4</v>
       </c>
       <c r="V7">
-        <v>5.742094167252284</v>
+        <v>0.6021683509120695</v>
       </c>
       <c r="W7">
-        <v>0.05792903692976104</v>
+        <v>0.2935189399686441</v>
       </c>
       <c r="X7">
-        <v>0.334892797429487</v>
+        <v>0.2364105524971075</v>
       </c>
       <c r="Y7">
-        <v>-0.276963760499726</v>
+        <v>0.0571083874715366</v>
       </c>
       <c r="Z7">
-        <v>0.5862282878411913</v>
+        <v>0.2271589081875973</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.09645665153360172</v>
+        <v>0.1467024797548192</v>
       </c>
       <c r="AC7">
-        <v>-0.09645665153360172</v>
+        <v>-0.1467024797548192</v>
       </c>
       <c r="AD7">
-        <v>841.5</v>
+        <v>11302.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>841.5</v>
+        <v>11302.9</v>
       </c>
       <c r="AG7">
-        <v>24.39999999999998</v>
+        <v>8031.5</v>
       </c>
       <c r="AH7">
-        <v>0.8553567798332995</v>
+        <v>0.6753806257319726</v>
       </c>
       <c r="AI7">
-        <v>0.7242447714949651</v>
+        <v>0.6239421925113026</v>
       </c>
       <c r="AJ7">
-        <v>0.1463707258548289</v>
+        <v>0.5965077761768245</v>
       </c>
       <c r="AK7">
-        <v>0.07076566125290018</v>
+        <v>0.5410640060900437</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.168</v>
+        <v>0.481</v>
       </c>
       <c r="E8">
-        <v>0.224</v>
+        <v>0.637</v>
       </c>
       <c r="F8">
-        <v>0.359</v>
+        <v>0.371</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1344,28 +1344,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>866.5</v>
+        <v>2098.4</v>
       </c>
       <c r="L8">
-        <v>0.3838146704464919</v>
+        <v>0.5670278595941309</v>
       </c>
       <c r="M8">
-        <v>56.3</v>
+        <v>54</v>
       </c>
       <c r="N8">
-        <v>0.02603468208092485</v>
+        <v>0.01012905162064826</v>
       </c>
       <c r="O8">
-        <v>0.0649740334679746</v>
+        <v>0.02573389248951582</v>
       </c>
       <c r="P8">
-        <v>56.3</v>
+        <v>54</v>
       </c>
       <c r="Q8">
-        <v>0.02603468208092485</v>
+        <v>0.01012905162064826</v>
       </c>
       <c r="R8">
-        <v>0.0649740334679746</v>
+        <v>0.02573389248951582</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1374,55 +1374,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>7992.3</v>
+        <v>6587.5</v>
       </c>
       <c r="V8">
-        <v>3.695861271676301</v>
+        <v>1.235650510204082</v>
       </c>
       <c r="W8">
-        <v>0.143109598995838</v>
+        <v>0.3341826984329214</v>
       </c>
       <c r="X8">
-        <v>0.4482178125016195</v>
+        <v>0.2556498960457627</v>
       </c>
       <c r="Y8">
-        <v>-0.3051082135057815</v>
+        <v>0.07853280238715871</v>
       </c>
       <c r="Z8">
-        <v>0.1295304978455571</v>
+        <v>0.2249077748673599</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.09761723996125668</v>
+        <v>0.1481846444259929</v>
       </c>
       <c r="AC8">
-        <v>-0.09761723996125668</v>
+        <v>-0.1481846444259929</v>
       </c>
       <c r="AD8">
-        <v>18277.7</v>
+        <v>12845.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>18277.7</v>
+        <v>12845.7</v>
       </c>
       <c r="AG8">
-        <v>10285.4</v>
+        <v>6258.200000000001</v>
       </c>
       <c r="AH8">
-        <v>0.8942035792213383</v>
+        <v>0.7067046636115069</v>
       </c>
       <c r="AI8">
-        <v>0.7442969418088529</v>
+        <v>0.6789625573479355</v>
       </c>
       <c r="AJ8">
-        <v>0.8262759180263338</v>
+        <v>0.5399934422834659</v>
       </c>
       <c r="AK8">
-        <v>0.6209228057254282</v>
+        <v>0.5074723688585075</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Türkiye Halk Bankasi A.S. (IBSE:HALKB)</t>
+          <t>Haci Ömer Sabanci Holding A.S. (IBSE:SAHOL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1448,13 +1448,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0454</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="E9">
-        <v>-0.179</v>
+        <v>0.598</v>
       </c>
       <c r="F9">
-        <v>0.405</v>
+        <v>0.228</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1469,82 +1469,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>122.3</v>
+        <v>1748.4</v>
       </c>
       <c r="L9">
-        <v>0.1015359070153591</v>
+        <v>0.3482244219163895</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>150.8</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.03067846607669617</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.08625028597574926</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.01710914454277286</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.04810112102493708</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>66.70000000000002</v>
+      </c>
+      <c r="T9">
+        <v>0.4423076923076924</v>
       </c>
       <c r="U9">
-        <v>4248.8</v>
+        <v>2802.1</v>
       </c>
       <c r="V9">
-        <v>5.028165680473373</v>
+        <v>0.5700539110975485</v>
       </c>
       <c r="W9">
-        <v>0.0226154813417656</v>
+        <v>0.3465540821787477</v>
       </c>
       <c r="X9">
-        <v>0.7584510592361865</v>
+        <v>0.2591908446097987</v>
       </c>
       <c r="Y9">
-        <v>-0.7358355778944209</v>
+        <v>0.08736323756894898</v>
       </c>
       <c r="Z9">
-        <v>0.05572673773040196</v>
+        <v>0.270027966010541</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.09895647905941082</v>
+        <v>0.1484268094110743</v>
       </c>
       <c r="AC9">
-        <v>-0.09895647905941082</v>
+        <v>-0.1484268094110743</v>
       </c>
       <c r="AD9">
-        <v>13014.3</v>
+        <v>12141.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>13014.3</v>
+        <v>12141.7</v>
       </c>
       <c r="AG9">
-        <v>8765.5</v>
+        <v>9339.6</v>
       </c>
       <c r="AH9">
-        <v>0.9390301097458025</v>
+        <v>0.7118225734587154</v>
       </c>
       <c r="AI9">
-        <v>0.7297997498976599</v>
+        <v>0.5771647779129905</v>
       </c>
       <c r="AJ9">
-        <v>0.912075334269809</v>
+        <v>0.6551760422585601</v>
       </c>
       <c r="AK9">
-        <v>0.6452859635303558</v>
+        <v>0.5121883003284946</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1561,7 +1564,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Türkiye Vakiflar Bankasi Türk Anonim Ortakligi (IBSE:VAKBN)</t>
+          <t>Türkiye Is Bankasi A.S. (IBSE:ISCTR)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1570,13 +1573,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.141</v>
+        <v>0.397</v>
       </c>
       <c r="E10">
-        <v>0.0911</v>
+        <v>0.486</v>
       </c>
       <c r="F10">
-        <v>0.249</v>
+        <v>0.399</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1591,28 +1594,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>389.7</v>
+        <v>2398.8</v>
       </c>
       <c r="L10">
-        <v>0.231853879105188</v>
+        <v>0.4131588012400965</v>
       </c>
       <c r="M10">
-        <v>0.068</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="N10">
-        <v>6.246555208524711e-05</v>
+        <v>0.01261667863370602</v>
       </c>
       <c r="O10">
-        <v>0.000174493199897357</v>
+        <v>0.03589294647323661</v>
       </c>
       <c r="P10">
-        <v>0.068</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Q10">
-        <v>6.246555208524711e-05</v>
+        <v>0.01261667863370602</v>
       </c>
       <c r="R10">
-        <v>0.000174493199897357</v>
+        <v>0.03589294647323661</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1621,55 +1624,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>6221.6</v>
+        <v>8486.9</v>
       </c>
       <c r="V10">
-        <v>5.71523057137608</v>
+        <v>1.243629383233445</v>
       </c>
       <c r="W10">
-        <v>0.0673126748885895</v>
+        <v>0.2849709540610856</v>
       </c>
       <c r="X10">
-        <v>1.155570276235754</v>
+        <v>0.2656596644392132</v>
       </c>
       <c r="Y10">
-        <v>-1.088257601347165</v>
+        <v>0.0193112896218724</v>
       </c>
       <c r="Z10">
-        <v>0.06355111917725348</v>
+        <v>0.2672964292079034</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.09959701895126299</v>
+        <v>0.1488480625755331</v>
       </c>
       <c r="AC10">
-        <v>-0.09959701895126299</v>
+        <v>-0.1488480625755331</v>
       </c>
       <c r="AD10">
-        <v>26450</v>
+        <v>17611.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>26450</v>
+        <v>17611.5</v>
       </c>
       <c r="AG10">
-        <v>20228.4</v>
+        <v>9124.6</v>
       </c>
       <c r="AH10">
-        <v>0.9604700311562679</v>
+        <v>0.7207253292300642</v>
       </c>
       <c r="AI10">
-        <v>0.8250670659429784</v>
+        <v>0.6730166615713848</v>
       </c>
       <c r="AJ10">
-        <v>0.9489327766571282</v>
+        <v>0.5721146912953244</v>
       </c>
       <c r="AK10">
-        <v>0.7829418959297735</v>
+        <v>0.5160651769403488</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1686,7 +1689,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Türkiye Is Bankasi A.S. (IBSE:ISCTR)</t>
+          <t>ICBC Turkey Bank A.S. (IBSE:ICBCT)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1695,13 +1698,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.16</v>
+        <v>0.531</v>
       </c>
       <c r="E11">
-        <v>0.147</v>
-      </c>
-      <c r="F11">
-        <v>0.352</v>
+        <v>0.774</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1716,85 +1716,82 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>966.4</v>
+        <v>68.2</v>
       </c>
       <c r="L11">
-        <v>0.2403860504452515</v>
+        <v>0.4608108108108108</v>
       </c>
       <c r="M11">
-        <v>123.3</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.05031420876520036</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.1275869205298013</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>123.3</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.05031420876520036</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.1275869205298013</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>10176.2</v>
+        <v>339.2</v>
       </c>
       <c r="V11">
-        <v>4.152534073288175</v>
+        <v>0.64072534945221</v>
       </c>
       <c r="W11">
-        <v>0.115393800448966</v>
+        <v>0.3749312809235844</v>
       </c>
       <c r="X11">
-        <v>0.4987532936606159</v>
+        <v>0.270660795846676</v>
       </c>
       <c r="Y11">
-        <v>-0.3833594932116499</v>
+        <v>0.1042704850769084</v>
       </c>
       <c r="Z11">
-        <v>0.1707247593452717</v>
+        <v>0.3312444046553268</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1147809694536887</v>
+        <v>0.1491563154998041</v>
       </c>
       <c r="AC11">
-        <v>-0.1147809694536887</v>
+        <v>-0.1491563154998041</v>
       </c>
       <c r="AD11">
-        <v>23486.9</v>
+        <v>1411.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>23486.9</v>
+        <v>1411.5</v>
       </c>
       <c r="AG11">
-        <v>13310.7</v>
+        <v>1072.3</v>
       </c>
       <c r="AH11">
-        <v>0.9055190361445784</v>
+        <v>0.727239940233912</v>
       </c>
       <c r="AI11">
-        <v>0.7148348571359004</v>
+        <v>0.9074252651880425</v>
       </c>
       <c r="AJ11">
-        <v>0.8445179014421399</v>
+        <v>0.6694761815570957</v>
       </c>
       <c r="AK11">
-        <v>0.5868863590268164</v>
+        <v>0.8816081558825948</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1811,7 +1808,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Albaraka Türk Katilim Bankasi A.S. (IBSE:ALBRK)</t>
+          <t>Türkiye Halk Bankasi A.S. (IBSE:HALKB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1820,10 +1817,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.115</v>
+        <v>0.25</v>
       </c>
       <c r="E12">
-        <v>0.00847</v>
+        <v>0.246</v>
+      </c>
+      <c r="F12">
+        <v>1.067</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1838,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>31.7</v>
+        <v>568.3</v>
       </c>
       <c r="L12">
-        <v>0.1544081831466147</v>
+        <v>0.340177181850832</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1865,60 +1865,182 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1375.3</v>
+        <v>7835.5</v>
       </c>
       <c r="V12">
-        <v>7.730747611017425</v>
+        <v>2.220191544826023</v>
       </c>
       <c r="W12">
-        <v>0.06068147013782542</v>
+        <v>0.11870248141031</v>
       </c>
       <c r="X12">
-        <v>0.3304454921127462</v>
+        <v>0.2718249115333956</v>
       </c>
       <c r="Y12">
-        <v>-0.2697640219749207</v>
+        <v>-0.1531224301230857</v>
       </c>
       <c r="Z12">
-        <v>0.286989171855211</v>
+        <v>0.1232633124525016</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.1165443765975069</v>
+        <v>0.1492260154633069</v>
       </c>
       <c r="AC12">
-        <v>-0.1165443765975069</v>
+        <v>-0.1492260154633069</v>
       </c>
       <c r="AD12">
-        <v>1034.3</v>
+        <v>9479.9</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1034.3</v>
+        <v>9479.9</v>
       </c>
       <c r="AG12">
-        <v>-341</v>
+        <v>1644.4</v>
       </c>
       <c r="AH12">
-        <v>0.8532420392674476</v>
+        <v>0.72871297783859</v>
       </c>
       <c r="AI12">
-        <v>0.6304400828965013</v>
+        <v>0.7024593747452818</v>
       </c>
       <c r="AJ12">
-        <v>2.090741876149602</v>
+        <v>0.3178444410081954</v>
       </c>
       <c r="AK12">
-        <v>-1.285337353938937</v>
+        <v>0.2905403017774479</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Türkiye Vakiflar Bankasi Türk Anonim Ortakligi (IBSE:VAKBN)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.382</v>
+      </c>
+      <c r="E13">
+        <v>0.381</v>
+      </c>
+      <c r="F13">
+        <v>0.608</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1029.4</v>
+      </c>
+      <c r="L13">
+        <v>0.3779278948527792</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>-0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>6513</v>
+      </c>
+      <c r="V13">
+        <v>1.441375647324392</v>
+      </c>
+      <c r="W13">
+        <v>0.1876036522024385</v>
+      </c>
+      <c r="X13">
+        <v>0.3144719087501595</v>
+      </c>
+      <c r="Y13">
+        <v>-0.126868256547721</v>
+      </c>
+      <c r="Z13">
+        <v>0.1059273504356602</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.1513461940091549</v>
+      </c>
+      <c r="AC13">
+        <v>-0.1513461940091549</v>
+      </c>
+      <c r="AD13">
+        <v>15432.9</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>15432.9</v>
+      </c>
+      <c r="AG13">
+        <v>8919.9</v>
+      </c>
+      <c r="AH13">
+        <v>0.7735207879106833</v>
+      </c>
+      <c r="AI13">
+        <v>0.7545395875502361</v>
+      </c>
+      <c r="AJ13">
+        <v>0.6637571157495256</v>
+      </c>
+      <c r="AK13">
+        <v>0.6398596883877077</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/turkey/turkey_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.397</v>
+        <v>0.536</v>
       </c>
       <c r="E2">
-        <v>0.493</v>
+        <v>0.6525</v>
       </c>
       <c r="F2">
-        <v>0.422</v>
+        <v>0.351</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>13373.3</v>
+        <v>15475.7</v>
       </c>
       <c r="L2">
-        <v>0.4433294878934946</v>
+        <v>0.4209139198572629</v>
       </c>
       <c r="M2">
-        <v>427.008</v>
+        <v>1535.82</v>
       </c>
       <c r="N2">
-        <v>0.008867752513348105</v>
+        <v>0.02090737193754824</v>
       </c>
       <c r="O2">
-        <v>0.03192989015426259</v>
+        <v>0.09924074516823149</v>
       </c>
       <c r="P2">
-        <v>360.308</v>
+        <v>1499.62</v>
       </c>
       <c r="Q2">
-        <v>0.007482581526761628</v>
+        <v>0.02041457534410679</v>
       </c>
       <c r="R2">
-        <v>0.0269423403348463</v>
+        <v>0.09690159411205956</v>
       </c>
       <c r="S2">
-        <v>66.70000000000002</v>
+        <v>36.2</v>
       </c>
       <c r="T2">
-        <v>0.156203162470024</v>
+        <v>0.0235704704978448</v>
       </c>
       <c r="U2">
-        <v>51234.4</v>
+        <v>61832.4</v>
       </c>
       <c r="V2">
-        <v>1.063994068893047</v>
+        <v>0.8417346984615761</v>
       </c>
       <c r="W2">
-        <v>0.2849709540610856</v>
+        <v>0.3942698958030209</v>
       </c>
       <c r="X2">
-        <v>0.2556498960457627</v>
+        <v>0.1839647963019199</v>
       </c>
       <c r="Y2">
-        <v>0.02932105801532287</v>
+        <v>0.210305099501101</v>
       </c>
       <c r="Z2">
-        <v>0.2225892327837866</v>
+        <v>0.4097021595263778</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1481846444259929</v>
+        <v>0.121318055835262</v>
       </c>
       <c r="AC2">
-        <v>-0.1481846444259929</v>
+        <v>-0.121318055835262</v>
       </c>
       <c r="AD2">
-        <v>96852.3</v>
+        <v>94190.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>96852.3</v>
+        <v>94190.7</v>
       </c>
       <c r="AG2">
-        <v>45617.9</v>
+        <v>32358.3</v>
       </c>
       <c r="AH2">
-        <v>0.6679229434530624</v>
+        <v>0.5618327577259632</v>
       </c>
       <c r="AI2">
-        <v>0.6618691122553927</v>
+        <v>0.6416041687953408</v>
       </c>
       <c r="AJ2">
-        <v>0.4864829989719614</v>
+        <v>0.3057960660236673</v>
       </c>
       <c r="AK2">
-        <v>0.4796981190803926</v>
+        <v>0.3808086371371477</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.42</v>
+        <v>0.573</v>
       </c>
       <c r="E3">
-        <v>0.493</v>
+        <v>0.674</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,10 +731,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>689.7</v>
+        <v>1108.7</v>
       </c>
       <c r="L3">
-        <v>0.4288645690834473</v>
+        <v>0.5064175763942813</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3918</v>
+        <v>4003.2</v>
       </c>
       <c r="V3">
-        <v>0.4090709766334649</v>
+        <v>0.1228073404627363</v>
       </c>
       <c r="W3">
-        <v>0.2831862040648738</v>
+        <v>0.5359922649262751</v>
       </c>
       <c r="X3">
-        <v>0.1604413138121452</v>
+        <v>0.1039180365367626</v>
       </c>
       <c r="Y3">
-        <v>0.1227448902527286</v>
+        <v>0.4320742283895125</v>
       </c>
       <c r="Z3">
-        <v>0.180350113826244</v>
+        <v>0.3885319798395685</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1355010849333974</v>
+        <v>0.1019206255951766</v>
       </c>
       <c r="AC3">
-        <v>-0.1355010849333974</v>
+        <v>-0.1019206255951766</v>
       </c>
       <c r="AD3">
-        <v>7484.3</v>
+        <v>7508.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7484.3</v>
+        <v>7508.9</v>
       </c>
       <c r="AG3">
-        <v>3566.3</v>
+        <v>3505.7</v>
       </c>
       <c r="AH3">
-        <v>0.4386505764237697</v>
+        <v>0.1872249496961824</v>
       </c>
       <c r="AI3">
-        <v>0.7834174220696297</v>
+        <v>0.7566404675534059</v>
       </c>
       <c r="AJ3">
-        <v>0.2713232553008574</v>
+        <v>0.09710246488528686</v>
       </c>
       <c r="AK3">
-        <v>0.6328388401888065</v>
+        <v>0.5920990406701797</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.38</v>
+        <v>0.531</v>
       </c>
       <c r="E4">
-        <v>0.469</v>
+        <v>0.619</v>
       </c>
       <c r="F4">
-        <v>0.489</v>
+        <v>0.404</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,28 +853,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2299.6</v>
+        <v>2806.7</v>
       </c>
       <c r="L4">
-        <v>0.5228859228268037</v>
+        <v>0.5234232218119429</v>
       </c>
       <c r="M4">
-        <v>70.59999999999999</v>
+        <v>320.2</v>
       </c>
       <c r="N4">
-        <v>0.01047104888467015</v>
+        <v>0.03863743318089125</v>
       </c>
       <c r="O4">
-        <v>0.03070099147677857</v>
+        <v>0.1140841557701215</v>
       </c>
       <c r="P4">
-        <v>70.59999999999999</v>
+        <v>320.2</v>
       </c>
       <c r="Q4">
-        <v>0.01047104888467015</v>
+        <v>0.03863743318089125</v>
       </c>
       <c r="R4">
-        <v>0.03070099147677857</v>
+        <v>0.1140841557701215</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>9332.799999999999</v>
+        <v>13117.2</v>
       </c>
       <c r="V4">
-        <v>1.384195538680588</v>
+        <v>1.582807428233562</v>
       </c>
       <c r="W4">
-        <v>0.2883619446499555</v>
+        <v>0.3961523804146848</v>
       </c>
       <c r="X4">
-        <v>0.1836293911594707</v>
+        <v>0.1316144843594952</v>
       </c>
       <c r="Y4">
-        <v>0.1047325534904848</v>
+        <v>0.2645378960551895</v>
       </c>
       <c r="Z4">
-        <v>0.4599505045190274</v>
+        <v>0.941735577467683</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1403369817751993</v>
+        <v>0.1125446335451287</v>
       </c>
       <c r="AC4">
-        <v>-0.1403369817751993</v>
+        <v>-0.1125446335451287</v>
       </c>
       <c r="AD4">
-        <v>7942.2</v>
+        <v>7420.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7942.2</v>
+        <v>7420.7</v>
       </c>
       <c r="AG4">
-        <v>-1390.599999999999</v>
+        <v>-5696.500000000001</v>
       </c>
       <c r="AH4">
-        <v>0.5408523214796453</v>
+        <v>0.4724153297682709</v>
       </c>
       <c r="AI4">
-        <v>0.5277349564108017</v>
+        <v>0.4856892274866317</v>
       </c>
       <c r="AJ4">
-        <v>-0.2598378115774131</v>
+        <v>-2.198741701404973</v>
       </c>
       <c r="AK4">
-        <v>-0.2432479708928071</v>
+        <v>-2.635438352995606</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Albaraka Türk Katilim Bankasi A.S. (IBSE:ALBRK)</t>
+          <t>Akbank T.A.S. (IBSE:AKBNK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +957,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.371</v>
+        <v>0.594</v>
       </c>
       <c r="E5">
-        <v>0.478</v>
+        <v>0.639</v>
+      </c>
+      <c r="F5">
+        <v>0.357</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,82 +978,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>71.90000000000001</v>
+        <v>2673.1</v>
       </c>
       <c r="L5">
-        <v>0.2828481510621558</v>
+        <v>0.5291695535979412</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>328.2</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05110716621507988</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.1227787961542778</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>328.2</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05110716621507988</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.1227787961542778</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>1340.4</v>
+        <v>3020.8</v>
       </c>
       <c r="V5">
-        <v>2.994638069705094</v>
+        <v>0.4703977078077798</v>
       </c>
       <c r="W5">
-        <v>0.1509235936188077</v>
+        <v>0.3923874111913569</v>
       </c>
       <c r="X5">
-        <v>0.1912788510663939</v>
+        <v>0.1649113777469474</v>
       </c>
       <c r="Y5">
-        <v>-0.04035525744758614</v>
+        <v>0.2274760334444095</v>
       </c>
       <c r="Z5">
-        <v>1.885113388606264</v>
+        <v>0.3403081400440585</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1415679062302372</v>
+        <v>0.1185812908445583</v>
       </c>
       <c r="AC5">
-        <v>-0.1415679062302372</v>
+        <v>-0.1185812908445583</v>
       </c>
       <c r="AD5">
-        <v>585.8</v>
+        <v>10884.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>585.8</v>
+        <v>10884.9</v>
       </c>
       <c r="AG5">
-        <v>-754.6000000000001</v>
+        <v>7864.099999999999</v>
       </c>
       <c r="AH5">
-        <v>0.5668666537642731</v>
+        <v>0.6289413926398446</v>
       </c>
       <c r="AI5">
-        <v>0.5308563661078387</v>
+        <v>0.6108969070429174</v>
       </c>
       <c r="AJ5">
-        <v>2.457980456026058</v>
+        <v>0.5504798437620311</v>
       </c>
       <c r="AK5">
-        <v>3.185310257492612</v>
+        <v>0.5314622459806314</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sekerbank T.A.S. (IBSE:SKBNK)</t>
+          <t>Türkiye Is Bankasi A.S. (IBSE:ISCTR)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1082,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.359</v>
+        <v>0.435</v>
       </c>
       <c r="E6">
-        <v>0.578</v>
+        <v>0.6659999999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.276</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1103,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>79.09999999999999</v>
+        <v>2753.6</v>
       </c>
       <c r="L6">
-        <v>0.2905951506245408</v>
+        <v>0.3718719191864627</v>
       </c>
       <c r="M6">
-        <v>0.108</v>
+        <v>431.6</v>
       </c>
       <c r="N6">
-        <v>0.0003550295857988166</v>
+        <v>0.05082849504787253</v>
       </c>
       <c r="O6">
-        <v>0.001365360303413401</v>
+        <v>0.1567402672864614</v>
       </c>
       <c r="P6">
-        <v>0.108</v>
+        <v>431.6</v>
       </c>
       <c r="Q6">
-        <v>0.0003550295857988166</v>
+        <v>0.05082849504787253</v>
       </c>
       <c r="R6">
-        <v>0.001365360303413401</v>
+        <v>0.1567402672864614</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>807.6</v>
+        <v>12300.2</v>
       </c>
       <c r="V6">
-        <v>2.65483234714004</v>
+        <v>1.448565001825398</v>
       </c>
       <c r="W6">
-        <v>0.2532010243277849</v>
+        <v>0.347975534549866</v>
       </c>
       <c r="X6">
-        <v>0.2327585668735655</v>
+        <v>0.1724189575010413</v>
       </c>
       <c r="Y6">
-        <v>0.02044245745421938</v>
+        <v>0.1755565770488247</v>
       </c>
       <c r="Z6">
-        <v>0.8081947743467931</v>
+        <v>0.4346427027665408</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1463846465027526</v>
+        <v>0.1207841127391726</v>
       </c>
       <c r="AC6">
-        <v>-0.1463846465027526</v>
+        <v>-0.1207841127391726</v>
       </c>
       <c r="AD6">
-        <v>613.9</v>
+        <v>15923.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>613.9</v>
+        <v>15923.5</v>
       </c>
       <c r="AG6">
-        <v>-193.7</v>
+        <v>3623.299999999999</v>
       </c>
       <c r="AH6">
-        <v>0.6686635442762227</v>
+        <v>0.6522068581352295</v>
       </c>
       <c r="AI6">
-        <v>0.6967427079786631</v>
+        <v>0.6361232177883598</v>
       </c>
       <c r="AJ6">
-        <v>-1.75294117647059</v>
+        <v>0.2990854010862926</v>
       </c>
       <c r="AK6">
-        <v>-2.635374149659866</v>
+        <v>0.2845843903894941</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Akbank T.A.S. (IBSE:AKBNK)</t>
+          <t>Yapi ve Kredi Bankasi A.S. (IBSE:YKBNK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1198,13 +1207,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.479</v>
+        <v>0.586</v>
       </c>
       <c r="E7">
-        <v>0.499</v>
+        <v>0.7140000000000001</v>
       </c>
       <c r="F7">
-        <v>0.422</v>
+        <v>0.255</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,28 +1228,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>2321.5</v>
+        <v>2412.6</v>
       </c>
       <c r="L7">
-        <v>0.5087550130393811</v>
+        <v>0.5129698928389181</v>
       </c>
       <c r="M7">
-        <v>65.40000000000001</v>
+        <v>288.6</v>
       </c>
       <c r="N7">
-        <v>0.01203821304323817</v>
+        <v>0.05170653050255308</v>
       </c>
       <c r="O7">
-        <v>0.0281714408787422</v>
+        <v>0.11962198458095</v>
       </c>
       <c r="P7">
-        <v>65.40000000000001</v>
+        <v>288.6</v>
       </c>
       <c r="Q7">
-        <v>0.01203821304323817</v>
+        <v>0.05170653050255308</v>
       </c>
       <c r="R7">
-        <v>0.0281714408787422</v>
+        <v>0.11962198458095</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1249,55 +1258,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3271.4</v>
+        <v>8886.700000000001</v>
       </c>
       <c r="V7">
-        <v>0.6021683509120695</v>
+        <v>1.592170563468602</v>
       </c>
       <c r="W7">
-        <v>0.2935189399686441</v>
+        <v>0.3972077248555294</v>
       </c>
       <c r="X7">
-        <v>0.2364105524971075</v>
+        <v>0.1882227417718164</v>
       </c>
       <c r="Y7">
-        <v>0.0571083874715366</v>
+        <v>0.208984983083713</v>
       </c>
       <c r="Z7">
-        <v>0.2271589081875973</v>
+        <v>0.3830216952244446</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1467024797548192</v>
+        <v>0.1210424969871394</v>
       </c>
       <c r="AC7">
-        <v>-0.1467024797548192</v>
+        <v>-0.1210424969871394</v>
       </c>
       <c r="AD7">
-        <v>11302.9</v>
+        <v>12585</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>11302.9</v>
+        <v>12585</v>
       </c>
       <c r="AG7">
-        <v>8031.5</v>
+        <v>3698.299999999999</v>
       </c>
       <c r="AH7">
-        <v>0.6753806257319726</v>
+        <v>0.6927586491619189</v>
       </c>
       <c r="AI7">
-        <v>0.6239421925113026</v>
+        <v>0.6801415948334099</v>
       </c>
       <c r="AJ7">
-        <v>0.5965077761768245</v>
+        <v>0.3985322959546542</v>
       </c>
       <c r="AK7">
-        <v>0.5410640060900437</v>
+        <v>0.3845665917976873</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1314,7 +1323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yapi ve Kredi Bankasi A.S. (IBSE:YKBNK)</t>
+          <t>Sekerbank T.A.S. (IBSE:SKBNK)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1323,13 +1332,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.481</v>
+        <v>0.412</v>
       </c>
       <c r="E8">
-        <v>0.637</v>
-      </c>
-      <c r="F8">
-        <v>0.371</v>
+        <v>0.7929999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1344,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>2098.4</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="L8">
-        <v>0.5670278595941309</v>
+        <v>0.3102785782901057</v>
       </c>
       <c r="M8">
-        <v>54</v>
+        <v>4.02</v>
       </c>
       <c r="N8">
-        <v>0.01012905162064826</v>
+        <v>0.01486136783733826</v>
       </c>
       <c r="O8">
-        <v>0.02573389248951582</v>
+        <v>0.0414860681114551</v>
       </c>
       <c r="P8">
-        <v>54</v>
+        <v>4.02</v>
       </c>
       <c r="Q8">
-        <v>0.01012905162064826</v>
+        <v>0.01486136783733826</v>
       </c>
       <c r="R8">
-        <v>0.02573389248951582</v>
+        <v>0.0414860681114551</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1374,55 +1380,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>6587.5</v>
+        <v>568.6</v>
       </c>
       <c r="V8">
-        <v>1.235650510204082</v>
+        <v>2.102033271719039</v>
       </c>
       <c r="W8">
-        <v>0.3341826984329214</v>
+        <v>0.3894694533762058</v>
       </c>
       <c r="X8">
-        <v>0.2556498960457627</v>
+        <v>0.1797068508320233</v>
       </c>
       <c r="Y8">
-        <v>0.07853280238715871</v>
+        <v>0.2097626025441825</v>
       </c>
       <c r="Z8">
-        <v>0.2249077748673599</v>
+        <v>5.667876588021777</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1481846444259929</v>
+        <v>0.1215936146833847</v>
       </c>
       <c r="AC8">
-        <v>-0.1481846444259929</v>
+        <v>-0.1215936146833847</v>
       </c>
       <c r="AD8">
-        <v>12845.7</v>
+        <v>554.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>12845.7</v>
+        <v>554.6</v>
       </c>
       <c r="AG8">
-        <v>6258.200000000001</v>
+        <v>-14</v>
       </c>
       <c r="AH8">
-        <v>0.7067046636115069</v>
+        <v>0.672160950187856</v>
       </c>
       <c r="AI8">
-        <v>0.6789625573479355</v>
+        <v>0.6069825982269892</v>
       </c>
       <c r="AJ8">
-        <v>0.5399934422834659</v>
+        <v>-0.05458089668615984</v>
       </c>
       <c r="AK8">
-        <v>0.5074723688585075</v>
+        <v>-0.04056795131845842</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1448,13 +1454,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.4429999999999999</v>
+        <v>0.541</v>
       </c>
       <c r="E9">
-        <v>0.598</v>
-      </c>
-      <c r="F9">
-        <v>0.228</v>
+        <v>0.636</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1469,85 +1472,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1748.4</v>
+        <v>1944</v>
       </c>
       <c r="L9">
-        <v>0.3482244219163895</v>
+        <v>0.3375527426160337</v>
       </c>
       <c r="M9">
-        <v>150.8</v>
+        <v>127</v>
       </c>
       <c r="N9">
-        <v>0.03067846607669617</v>
+        <v>0.03044906375122875</v>
       </c>
       <c r="O9">
-        <v>0.08625028597574926</v>
+        <v>0.06532921810699588</v>
       </c>
       <c r="P9">
-        <v>84.09999999999999</v>
+        <v>127</v>
       </c>
       <c r="Q9">
-        <v>0.01710914454277286</v>
+        <v>0.03044906375122875</v>
       </c>
       <c r="R9">
-        <v>0.04810112102493708</v>
+        <v>0.06532921810699588</v>
       </c>
       <c r="S9">
-        <v>66.70000000000002</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.4423076923076924</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2802.1</v>
+        <v>2812.5</v>
       </c>
       <c r="V9">
-        <v>0.5700539110975485</v>
+        <v>0.6743148960655974</v>
       </c>
       <c r="W9">
-        <v>0.3465540821787477</v>
+        <v>0.4417077548794619</v>
       </c>
       <c r="X9">
-        <v>0.2591908446097987</v>
+        <v>0.2107054019192965</v>
       </c>
       <c r="Y9">
-        <v>0.08736323756894898</v>
+        <v>0.2310023529601654</v>
       </c>
       <c r="Z9">
-        <v>0.270027966010541</v>
+        <v>0.4264989039635049</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1484268094110743</v>
+        <v>0.1227283275404103</v>
       </c>
       <c r="AC9">
-        <v>-0.1484268094110743</v>
+        <v>-0.1227283275404103</v>
       </c>
       <c r="AD9">
-        <v>12141.7</v>
+        <v>11656.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>12141.7</v>
+        <v>11656.2</v>
       </c>
       <c r="AG9">
-        <v>9339.6</v>
+        <v>8843.700000000001</v>
       </c>
       <c r="AH9">
-        <v>0.7118225734587154</v>
+        <v>0.7364709896317077</v>
       </c>
       <c r="AI9">
-        <v>0.5771647779129905</v>
+        <v>0.5468338040326893</v>
       </c>
       <c r="AJ9">
-        <v>0.6551760422585601</v>
+        <v>0.6795214605135771</v>
       </c>
       <c r="AK9">
-        <v>0.5121883003284946</v>
+        <v>0.4779525814314203</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1564,7 +1567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Türkiye Is Bankasi A.S. (IBSE:ISCTR)</t>
+          <t>Türkiye Halk Bankasi A.S. (IBSE:HALKB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1573,13 +1576,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.397</v>
+        <v>0.427</v>
       </c>
       <c r="E10">
-        <v>0.486</v>
+        <v>0.399</v>
       </c>
       <c r="F10">
-        <v>0.399</v>
+        <v>0.345</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1594,85 +1597,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>2398.8</v>
+        <v>612.1</v>
       </c>
       <c r="L10">
-        <v>0.4131588012400965</v>
+        <v>0.258673879051684</v>
       </c>
       <c r="M10">
-        <v>86.09999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.01261667863370602</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.03589294647323661</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>86.09999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.01261667863370602</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.03589294647323661</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>8486.9</v>
+        <v>5895.5</v>
       </c>
       <c r="V10">
-        <v>1.243629383233445</v>
+        <v>2.025457793657883</v>
       </c>
       <c r="W10">
-        <v>0.2849709540610856</v>
+        <v>0.1533124608641202</v>
       </c>
       <c r="X10">
-        <v>0.2656596644392132</v>
+        <v>0.2012743354882414</v>
       </c>
       <c r="Y10">
-        <v>0.0193112896218724</v>
+        <v>-0.04796187462412116</v>
       </c>
       <c r="Z10">
-        <v>0.2672964292079034</v>
+        <v>0.4197874718373575</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1488480625755331</v>
+        <v>0.1235240163404744</v>
       </c>
       <c r="AC10">
-        <v>-0.1488480625755331</v>
+        <v>-0.1235240163404744</v>
       </c>
       <c r="AD10">
-        <v>17611.5</v>
+        <v>7475.2</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>17611.5</v>
+        <v>7475.2</v>
       </c>
       <c r="AG10">
-        <v>9124.6</v>
+        <v>1579.7</v>
       </c>
       <c r="AH10">
-        <v>0.7207253292300642</v>
+        <v>0.719745038947034</v>
       </c>
       <c r="AI10">
-        <v>0.6730166615713848</v>
+        <v>0.6230319800635101</v>
       </c>
       <c r="AJ10">
-        <v>0.5721146912953244</v>
+        <v>0.3517949403171209</v>
       </c>
       <c r="AK10">
-        <v>0.5160651769403488</v>
+        <v>0.2588568806738111</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.531</v>
+        <v>0.5770000000000001</v>
       </c>
       <c r="E11">
-        <v>0.774</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>68.2</v>
+        <v>61.9</v>
       </c>
       <c r="L11">
-        <v>0.4608108108108108</v>
+        <v>0.4440459110473458</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1743,55 +1743,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>339.2</v>
+        <v>528.6</v>
       </c>
       <c r="V11">
-        <v>0.64072534945221</v>
+        <v>1.254390128144281</v>
       </c>
       <c r="W11">
-        <v>0.3749312809235844</v>
+        <v>0.4298611111111111</v>
       </c>
       <c r="X11">
-        <v>0.270660795846676</v>
+        <v>0.2735305277241424</v>
       </c>
       <c r="Y11">
-        <v>0.1042704850769084</v>
+        <v>0.1563305833869686</v>
       </c>
       <c r="Z11">
-        <v>0.3312444046553268</v>
+        <v>0.1146098824303215</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1491563154998041</v>
+        <v>0.1256195119578269</v>
       </c>
       <c r="AC11">
-        <v>-0.1491563154998041</v>
+        <v>-0.1256195119578269</v>
       </c>
       <c r="AD11">
-        <v>1411.5</v>
+        <v>1813.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1411.5</v>
+        <v>1813.4</v>
       </c>
       <c r="AG11">
-        <v>1072.3</v>
+        <v>1284.8</v>
       </c>
       <c r="AH11">
-        <v>0.727239940233912</v>
+        <v>0.8114372650796492</v>
       </c>
       <c r="AI11">
-        <v>0.9074252651880425</v>
+        <v>0.9082895066366141</v>
       </c>
       <c r="AJ11">
-        <v>0.6694761815570957</v>
+        <v>0.7530184034696987</v>
       </c>
       <c r="AK11">
-        <v>0.8816081558825948</v>
+        <v>0.8752639825601199</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Türkiye Halk Bankasi A.S. (IBSE:HALKB)</t>
+          <t>Türkiye Vakiflar Bankasi Türk Anonim Ortakligi (IBSE:VAKBN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.25</v>
+        <v>0.506</v>
       </c>
       <c r="E12">
-        <v>0.246</v>
+        <v>0.455</v>
       </c>
       <c r="F12">
-        <v>1.067</v>
+        <v>0.444</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1838,19 +1838,19 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>568.3</v>
+        <v>1006.1</v>
       </c>
       <c r="L12">
-        <v>0.340177181850832</v>
+        <v>0.2892006093880249</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>36.2</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.008407850423876437</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.03598051883510586</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1862,185 +1862,66 @@
         <v>-0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>36.2</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>7835.5</v>
+        <v>10699.1</v>
       </c>
       <c r="V12">
-        <v>2.220191544826023</v>
+        <v>2.484984322378353</v>
       </c>
       <c r="W12">
-        <v>0.11870248141031</v>
+        <v>0.2044170831809501</v>
       </c>
       <c r="X12">
-        <v>0.2718249115333956</v>
+        <v>0.2719882886833823</v>
       </c>
       <c r="Y12">
-        <v>-0.1531224301230857</v>
+        <v>-0.06757120550243226</v>
       </c>
       <c r="Z12">
-        <v>0.1232633124525016</v>
+        <v>0.2513490803711605</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.1492260154633069</v>
+        <v>0.1271900116117019</v>
       </c>
       <c r="AC12">
-        <v>-0.1492260154633069</v>
+        <v>-0.1271900116117019</v>
       </c>
       <c r="AD12">
-        <v>9479.9</v>
+        <v>18368.3</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>9479.9</v>
+        <v>18368.3</v>
       </c>
       <c r="AG12">
-        <v>1644.4</v>
+        <v>7669.199999999999</v>
       </c>
       <c r="AH12">
-        <v>0.72871297783859</v>
+        <v>0.8101112297012411</v>
       </c>
       <c r="AI12">
-        <v>0.7024593747452818</v>
+        <v>0.7645589747218489</v>
       </c>
       <c r="AJ12">
-        <v>0.3178444410081954</v>
+        <v>0.6404502826793155</v>
       </c>
       <c r="AK12">
-        <v>0.2905403017774479</v>
+        <v>0.5755238038062076</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Türkiye Vakiflar Bankasi Türk Anonim Ortakligi (IBSE:VAKBN)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.382</v>
-      </c>
-      <c r="E13">
-        <v>0.381</v>
-      </c>
-      <c r="F13">
-        <v>0.608</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>1029.4</v>
-      </c>
-      <c r="L13">
-        <v>0.3779278948527792</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>-0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>-0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>6513</v>
-      </c>
-      <c r="V13">
-        <v>1.441375647324392</v>
-      </c>
-      <c r="W13">
-        <v>0.1876036522024385</v>
-      </c>
-      <c r="X13">
-        <v>0.3144719087501595</v>
-      </c>
-      <c r="Y13">
-        <v>-0.126868256547721</v>
-      </c>
-      <c r="Z13">
-        <v>0.1059273504356602</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.1513461940091549</v>
-      </c>
-      <c r="AC13">
-        <v>-0.1513461940091549</v>
-      </c>
-      <c r="AD13">
-        <v>15432.9</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>15432.9</v>
-      </c>
-      <c r="AG13">
-        <v>8919.9</v>
-      </c>
-      <c r="AH13">
-        <v>0.7735207879106833</v>
-      </c>
-      <c r="AI13">
-        <v>0.7545395875502361</v>
-      </c>
-      <c r="AJ13">
-        <v>0.6637571157495256</v>
-      </c>
-      <c r="AK13">
-        <v>0.6398596883877077</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
         <v>0</v>
       </c>
     </row>
